--- a/DADOS EXTERNOS.xlsx
+++ b/DADOS EXTERNOS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\autobras\Indicadores Atb\FINANCEIRO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\autobras\GITHUB Indicadores Atb\FINANCEIRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387FD979-E97D-4329-8441-6BDEDCF6548A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2843F53-01BC-4EC6-94F6-BDE5FC8DFE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{677CDEDD-A89D-4E35-B452-0764E7A83DD0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{677CDEDD-A89D-4E35-B452-0764E7A83DD0}"/>
   </bookViews>
   <sheets>
     <sheet name="TIPO" sheetId="5" r:id="rId1"/>
@@ -419,7 +419,7 @@
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,6 +451,13 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -515,12 +522,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -537,8 +545,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Moeda" xfId="3" builtinId="4"/>
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{6DB9D202-E376-4AB1-A650-FA8CAF981972}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2D98EC64-5642-4C6C-BC0D-843C433C0692}"/>
@@ -29582,7 +29592,7 @@
         <v>2026</v>
       </c>
       <c r="C20" s="8">
-        <v>1389098.33</v>
+        <v>1547563.71</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -29592,7 +29602,9 @@
       <c r="B21" s="4">
         <v>2026</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="14">
+        <v>1132353.1200000001</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
@@ -29862,7 +29874,7 @@
         <v>2026</v>
       </c>
       <c r="C20" s="8">
-        <v>905787.58</v>
+        <v>1013081.97</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -29872,7 +29884,9 @@
       <c r="B21" s="4">
         <v>2026</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="8">
+        <v>740946.73</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
@@ -30158,7 +30172,9 @@
       <c r="B21" s="4">
         <v>2026</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3">
+        <v>1557203.62</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">

--- a/DADOS EXTERNOS.xlsx
+++ b/DADOS EXTERNOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\autobras\GITHUB Indicadores Atb\FINANCEIRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2843F53-01BC-4EC6-94F6-BDE5FC8DFE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5571C6-BE42-430C-84E1-DB7A4265A338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{677CDEDD-A89D-4E35-B452-0764E7A83DD0}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7203" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7215" uniqueCount="133">
   <si>
     <t>ação social</t>
   </si>
@@ -410,6 +410,24 @@
   <si>
     <t>DESPESAS VIAGEM CHINA</t>
   </si>
+  <si>
+    <t>GALPÃO GOIANIA</t>
+  </si>
+  <si>
+    <t>LANCHE</t>
+  </si>
+  <si>
+    <t>LOJA CONECT</t>
+  </si>
+  <si>
+    <t>MÃO DE OBRA</t>
+  </si>
+  <si>
+    <t>Viagem china</t>
+  </si>
+  <si>
+    <t>garantia</t>
+  </si>
 </sst>
 </file>
 
@@ -528,7 +546,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -546,6 +564,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moeda" xfId="3" builtinId="4"/>
@@ -863,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE394A55-AB2B-44EE-B3DD-F68ADECBE364}">
-  <dimension ref="A1:B3561"/>
+  <dimension ref="A1:B3567"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52" style="1" bestFit="1" customWidth="1"/>
@@ -29356,6 +29377,54 @@
         <v>126</v>
       </c>
       <c r="B3561" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3562" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3562" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3562" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3563" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3563" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3563" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3564" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3564" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3564" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3565" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3565" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3565" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3566" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3566" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3566" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3567" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3567" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3567" s="12" t="s">
         <v>1</v>
       </c>
     </row>

--- a/DADOS EXTERNOS.xlsx
+++ b/DADOS EXTERNOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samuel\Desktop\CONSULT\autobras\GITHUB Indicadores Atb\FINANCEIRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5571C6-BE42-430C-84E1-DB7A4265A338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01000AB6-9BCC-48D5-8033-D2E32D88A5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{677CDEDD-A89D-4E35-B452-0764E7A83DD0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{677CDEDD-A89D-4E35-B452-0764E7A83DD0}"/>
   </bookViews>
   <sheets>
     <sheet name="TIPO" sheetId="5" r:id="rId1"/>
@@ -29682,7 +29682,9 @@
       <c r="B22" s="4">
         <v>2026</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="8">
+        <v>1330548.25</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
@@ -29964,7 +29966,9 @@
       <c r="B22" s="4">
         <v>2026</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="8">
+        <v>863485.25</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
@@ -30252,7 +30256,9 @@
       <c r="B22" s="4">
         <v>2026</v>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3">
+        <v>1320648.4099999999</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
